--- a/tame_output/ON/bt/strategyON_20231110.xlsx
+++ b/tame_output/ON/bt/strategyON_20231110.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,11 +610,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>89.1%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>22.9%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -916,11 +916,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.5%</t>
+          <t>103.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,16 +1064,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>98.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>27.4%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.8%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.9%</t>
+          <t>133.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,16 +1370,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>126.8%</t>
+          <t>127.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>27.6%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1776"/>
+  <dimension ref="A1:G1777"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42358,7 +42358,7 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.122172992355287</v>
+        <v>3.125945945239774</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
@@ -42374,6 +42374,29 @@
       </c>
       <c r="G1776" t="n">
         <v>4.365827362016724</v>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" s="2" t="n">
+        <v>45239</v>
+      </c>
+      <c r="B1777" t="n">
+        <v>3.126357332773642</v>
+      </c>
+      <c r="C1777" t="n">
+        <v>3.084316661211631</v>
+      </c>
+      <c r="D1777" t="n">
+        <v>1.534969793600102</v>
+      </c>
+      <c r="E1777" t="n">
+        <v>3.697948154337925</v>
+      </c>
+      <c r="F1777" t="n">
+        <v>2.170782106193299</v>
+      </c>
+      <c r="G1777" t="n">
+        <v>4.386785924927612</v>
       </c>
     </row>
   </sheetData>
